--- a/Debuggers/设定.xlsx
+++ b/Debuggers/设定.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18912FA-DD67-4C2D-AC59-361A5CDAFA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色" sheetId="1" r:id="rId1"/>
@@ -2843,15 +2843,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2864,7 +2856,15 @@
     <xf numFmtId="49" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5236,7 +5236,7 @@
     <col min="4" max="16384" width="19" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="51" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>332</v>
       </c>
@@ -5248,7 +5248,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="52" t="s">
         <v>393</v>
       </c>
       <c r="B2" s="47" t="s">
@@ -5259,7 +5259,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="54"/>
+      <c r="A3" s="52"/>
       <c r="B3" s="47" t="s">
         <v>26</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="C4" s="38"/>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="53" t="s">
         <v>394</v>
       </c>
       <c r="B5" s="47" t="s">
@@ -5284,7 +5284,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="56"/>
+      <c r="A6" s="54"/>
       <c r="B6" s="47" t="s">
         <v>32</v>
       </c>
@@ -5293,7 +5293,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="56"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="47" t="s">
         <v>395</v>
       </c>
@@ -5302,7 +5302,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="57"/>
+      <c r="A8" s="55"/>
       <c r="B8" s="47" t="s">
         <v>209</v>
       </c>
@@ -5315,7 +5315,7 @@
       <c r="C9" s="38"/>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="53" t="s">
         <v>397</v>
       </c>
       <c r="B10" s="47" t="s">
@@ -5326,7 +5326,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="56"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="47" t="s">
         <v>210</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="56"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="47" t="s">
         <v>35</v>
       </c>
@@ -5344,7 +5344,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="56"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="47" t="s">
         <v>211</v>
       </c>
@@ -5353,7 +5353,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="56"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="47" t="s">
         <v>212</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="56"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="47" t="s">
         <v>213</v>
       </c>
@@ -5371,7 +5371,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="56"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="47" t="s">
         <v>214</v>
       </c>
@@ -5380,7 +5380,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="56"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="47" t="s">
         <v>215</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="56"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="47" t="s">
         <v>216</v>
       </c>
@@ -5398,7 +5398,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="56"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="47" t="s">
         <v>217</v>
       </c>
@@ -5407,7 +5407,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="56"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="47" t="s">
         <v>47</v>
       </c>
@@ -5416,7 +5416,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="56"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="47" t="s">
         <v>53</v>
       </c>
@@ -5425,7 +5425,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="57"/>
+      <c r="A22" s="55"/>
       <c r="B22" s="47" t="s">
         <v>118</v>
       </c>
@@ -5434,7 +5434,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="53" t="s">
         <v>398</v>
       </c>
       <c r="B24" s="47" t="s">
@@ -5445,7 +5445,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="56"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="47" t="s">
         <v>62</v>
       </c>
@@ -5454,7 +5454,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="56"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="47" t="s">
         <v>63</v>
       </c>
@@ -5463,7 +5463,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="56"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="47" t="s">
         <v>218</v>
       </c>
@@ -5472,7 +5472,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="57"/>
+      <c r="A28" s="55"/>
       <c r="B28" s="47" t="s">
         <v>219</v>
       </c>
@@ -5519,16 +5519,16 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="53" t="s">
         <v>223</v>
       </c>
       <c r="B2" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="56" t="s">
         <v>390</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="53" t="s">
         <v>402</v>
       </c>
       <c r="E2" s="36" t="s">
@@ -5539,12 +5539,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56"/>
+      <c r="A3" s="54"/>
       <c r="B3" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="56"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="36" t="s">
         <v>221</v>
       </c>
@@ -5553,15 +5553,15 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="56"/>
+      <c r="A4" s="54"/>
       <c r="B4" s="36" t="s">
         <v>225</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="51" t="s">
+      <c r="D4" s="54"/>
+      <c r="E4" s="56" t="s">
         <v>222</v>
       </c>
       <c r="F4" s="36" t="s">
@@ -5569,41 +5569,41 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="56"/>
+      <c r="A5" s="54"/>
       <c r="B5" s="36" t="s">
         <v>226</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="52"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="57"/>
       <c r="F5" s="36" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="56"/>
+      <c r="A6" s="54"/>
       <c r="B6" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="56" t="s">
         <v>391</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="53"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="36" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="57"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="51" t="s">
+      <c r="C7" s="58"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="56" t="s">
         <v>228</v>
       </c>
       <c r="F7" s="36" t="s">
@@ -5611,22 +5611,22 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="56"/>
-      <c r="E8" s="52"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="36" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="56"/>
-      <c r="E9" s="53"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="36" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="56"/>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="54"/>
+      <c r="E10" s="56" t="s">
         <v>229</v>
       </c>
       <c r="F10" s="36" t="s">
@@ -5634,22 +5634,22 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="56"/>
-      <c r="E11" s="52"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="36" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="56"/>
-      <c r="E12" s="53"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="36" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="56"/>
-      <c r="E13" s="51" t="s">
+      <c r="D13" s="54"/>
+      <c r="E13" s="56" t="s">
         <v>230</v>
       </c>
       <c r="F13" s="36" t="s">
@@ -5657,21 +5657,21 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="56"/>
-      <c r="E14" s="52"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="57"/>
       <c r="F14" s="36" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="56"/>
-      <c r="E15" s="53"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="58"/>
       <c r="F15" s="36" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="57"/>
+      <c r="D16" s="55"/>
       <c r="E16" s="36" t="s">
         <v>231</v>
       </c>

--- a/Debuggers/设定.xlsx
+++ b/Debuggers/设定.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\ArkWars\Debuggers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18912FA-DD67-4C2D-AC59-361A5CDAFA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A2B946-B6F2-4401-8C0B-65E1F1136B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="413">
   <si>
     <t>名称</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -253,10 +253,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段开始时，你可以令本回合内你的所有指向类回复卡牌被视为【杀·物理】或【杀·法术】使用或打出，以此法使用的卡牌无次数限制且造成的伤害+1，若造成伤害则选择一名其他角色回复等量生命值。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>沉睡</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -278,11 +274,6 @@
   </si>
   <si>
     <t>光影迅捷剑</t>
-  </si>
-  <si>
-    <t>你的攻击范围始终为2。当场上有“灼燃损伤”触发时，你可以令其下一回合的出【杀】次数-1。
-修改：你的攻击范围始终为3。当场上有“灼燃损伤”触发时，你可以令其下一回合的出【杀】次数-1并对其造成1点真实伤害。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>出牌阶段限一次，你可以弃置1张红色【杀】，视为使用2张不计次数的【杀·灼燃】，若造成伤害则进行判定，判定结果为方片时获得“屏障”。
@@ -327,14 +318,6 @@
   </si>
   <si>
     <t>令其下一次受到的伤害至多为1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏开始时，你获得“屏障”。当场上有“屏障”触发时，你与其各摸1张牌。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏开始时，将投递坐标置入你的宝物栏。持有“投递坐标”的角色进入濒死状态时，你可以将“投递坐标”移出游戏并将对应角色的血量回复至其中“快递”数量。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -391,20 +374,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>准备阶段，你可以摸一张牌并选择其中一个策略触发：
-①：本回合攻击范围+1且你使用的【杀】伤害+1
-②：可以额外使用一张【杀】且【杀】可以额外指定一名目标</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>你能指定拥有“沉睡”的角色为目标。每回合限一次，当有角色失去“沉睡”时，你从牌堆中抽取一张指向类回复卡牌。你可以弃置2张手牌令一名其他角色获得“沉睡”。若该角色已经拥有“沉睡”，则对其造成1点法术伤害。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段限一次，你可以失去至多3个自己的“弹药”，并选择X个攻击范围内的角色对其造成1点物理伤害。（X为“弹药”失去数量）当你造成伤害时，你可以失去1个自己的“弹药”令此次伤害+1。弃牌阶段结束时，你可以弃置任意张【杀】并获得等量“弹药”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>出牌阶段限一次，你可将一张手牌移出游戏并扣置于【投递坐标】下，称为“快递”，若如此做，你可将宝物栏里的【投递坐标】置入一名其他角色的宝物栏；你能将“快递”如手牌般使用或打出。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -425,10 +398,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段限一次，你可以弃置2张手牌并选择一名角色，令其获得“屏障”，以此法获得的“屏障”失效后，其回复1点血量并获得“庇护”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>当你对其他干员造成伤害时，可以摸1张牌并将1张手牌置于其干员牌上称之为“心烛”。拥有“心烛”的干员受到伤害时，你摸一张牌，其死亡时，你收回“心烛”并增加一点体力上限。你的【杀】可以指定任意名拥有“心烛”的干员作为目标。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -438,10 +407,6 @@
   </si>
   <si>
     <t>游戏开始或回合开始时，若“血镰”不在场上，则你可以失去一点血量将“血镰”置入你的武器栏，若“血镰”在场上，则你可以移动“血镰”。当“血镰”持有者血量产生变化时，你摸1张牌。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏开始时，你获得“屏障”，当你失去屏障时，回复1点血量并摸1张牌。每回合结束时，若你本回合没有受到伤害，则你可以弃置2张手牌获得“屏障”。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -463,10 +428,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段，对你自己使用，抽取三张卡牌，弃置其中一张。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>出牌阶段，选择一名角色，令其抽取两张卡牌，弃置其中一张。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -475,25 +436,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段限一次，你可以弃置X张牌并失去“屏障”，然后令攻击范围内的X名角色获得“晕眩”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>隐狐之艺</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段，你可以选择其中一个策略触发并移除：
-①：你可以令一名攻击范围内的角色获得“沉默”并视为对其使用1张不计次数的【杀·法术】。
-②：你可以令一名攻击范围内的角色在本回合内受到的法术伤害+1，并视为对其使用1张不计次数的【杀·法术】。
-③：你可以令X名攻击范围内的角色获得“晕眩”，并视为对其中任意数量目标使用至多2张不计次数的【杀·法术】。（X为你的攻击范围）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏开始时，将【机动盾牌】置入你的宝物区。回合开始时，你可以弃置2张手牌将【机动盾牌】置入你的宝物区，若你的宝物区有【机动盾牌】，则获得1点护甲。当你的护甲减少时，抽一张牌。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>锁定技：回合开始时，获得1点护甲。出牌阶段，你可以移除全部护甲并对一名攻击范围内的角色造成等量伤害，随后销毁机动盾牌。此宝物离开宝物区时销毁。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -502,10 +448,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>每回合限一次，当你使用或打出一张牌后，可以摸一张牌展示并交给场上任意一名角色，若展示牌与使用牌类型相同，此技能视为未发动过。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>主动技</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -534,10 +476,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段，你令下一张指向性卡牌额外选择至多两个目标，该卡牌造成伤害时令对应目标获得“晕眩”，在该卡牌结算后你流失X点体力。（X为该卡牌选择目标数减去造成伤害数）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>浮空</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -578,30 +516,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>当一名角色获得“浮空”后，你可以对其造成X点伤害并摸X张牌。（X为你与其距离-1且至多为3。）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>游戏开始时，你获得屏障，当你的“屏障”触发时，你摸1张牌。每回合限一次，一名角色使用【杀】造成伤害后，你可以弃置一张手牌视为使用【杀·物理】，若你本次使用的【杀·物理】造成伤害，则你获得“屏障”。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>准备阶段，将【兰登战术】置入你的武器栏。出牌阶段限一次，你可以弃置至多X张【杀】视为使用X张不计入次数的【杀·物理】，以此法转化的【杀·物理】造成伤害后，你摸1张牌。（X为你的血量除以2向上取整）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>你造成血量回复时摸1张牌，若目标角色拥有负面标记则随机移除1个并摸1张牌。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段限一次，你展示一名其他角色的一张手牌并获得，若为红色，则令该角色回复1点血量且此技能视为未发动过，若为黑色，则你令其下次受到伤害后摸2张牌。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏开始时，你将3个【白铁™多功能平台】置入场上角色的宝物栏。（每名角色至多获得一个【白铁™多功能平台】）当【白铁™多功能平台】销毁时，你摸X张牌。（X为【白铁™多功能平台】升级次数）回合开始时，你可以弃置3张手牌将【白铁™多功能平台】置入一名角色的宝物栏。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>你的手牌上限+2。此宝物离开宝物区时销毁。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -618,10 +536,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>游戏开始时，你获得“屏障”。当你失去屏障时，你可以视为对攻击范围内任意名角色使用一张【杀】。回合开始或回合结束时，若你没有“屏障”，则可以弃置2张手牌获得“屏障”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>8</t>
     </r>
@@ -639,10 +553,6 @@
   </si>
   <si>
     <t>策略技</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前回合结束时，若你的血量与手牌数均未发生变动，则你可以摸X张牌并将手牌中的X张牌以任意顺序放回牌堆顶。（X为你的体力上限）</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -673,22 +583,6 @@
   </si>
   <si>
     <t>功能卡牌</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段，对除你以外任意一名角色使用。将“旧日残影”置入该角色的判定区内，其需弃置一张与判定结果相同花色的手牌，若没有弃置则对其造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点法术伤害。</t>
-    </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -824,10 +718,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>出牌阶段限一次，你令下一张使用的卡牌指定攻击范围内的所有角色且不可响应，若该卡牌造成伤害，则令目标获得“眩晕”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>游戏开始时你获得3个“微尘”。每回合限一次，拥有“微尘”的角色受到伤害时，其摸X</t>
     </r>
@@ -940,22 +830,6 @@
   </si>
   <si>
     <r>
-      <t>出牌阶段，使用后你失去</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量，令本回合你下一次造成的伤害翻倍。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>你或拥有“应急储备”的角色造成伤害时，你可以失去</t>
     </r>
     <r>
@@ -1015,35 +889,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>当你造成伤害时，你摸一张牌后弃置一张手牌并令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你造成伤害时，你令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。你无法获得“冻结”且对“冻结”角色造成的伤害+1。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>冰焰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段，对攻击范围内的一名角色使用。获取其</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张手牌并进行三次判定，当判定结果为黑色时获得“寒冷”。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段，对所有角色使用。目标角色需要依次打出一张【闪】，否则该角色受到一点法术伤害。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -1175,22 +1021,6 @@
   </si>
   <si>
     <r>
-      <t>准备阶段，将【悲叹的仆役】置入你的宝物栏，你拥有【悲叹的仆役】时其他角色距离你+1。当你对其他角色造成伤害时，你将【悲叹的仆役】置入其宝物栏并可以获取其一张卡牌（每回合每名角色限制一次）拥有【悲叹的仆役】的角色受到或受到伤害时，你摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>若你通过“噩愿”获得的卡牌数量不小于</t>
     </r>
     <r>
@@ -1211,26 +1041,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>当你杀死一名角色时，你获得其所有卡牌并将“蓝莓与黑巧”重置为游戏开始时的状态。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当你造成伤害时，你令目标获得“寒冷”，当场上有角色获得“冻结”时候，你摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2张牌。你无法获得“冻结”。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>出牌阶段限一次，你可以弃置所有伤害类卡牌视为对至多X名角色使用“冰焰”。（X为你弃置的卡牌数）若所有“冰焰”结算后你的手牌颜色一致，则你视为使用</t>
     </r>
@@ -1247,26 +1057,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>你令所有拥有“迷狂牢笼”的角色打出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张杀，若有角色拒绝，则你对其造成1点法术伤害。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前回合结束时，若你本回合触发过“灼痕”，则你可以选择至多两名角色，令其各视为使用一张【杀·法术】，若该【杀·法术】令一名角色进入濒死，则你视为使用一张【杀·法术】。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>每回合限一次，当有卡牌进入弃牌堆时，你摸一张与其类型相同的卡牌，以此法获得的非装备卡牌使用不计次数且可以额外指定一个目标。当你造成伤害后，你可以令目标下一次受到的法术伤害+1，若该伤害为法术伤害，则你可以选择一名角色回复等量血量。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -1436,87 +1226,6 @@
   </si>
   <si>
     <t>汹涌怒火</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每回合限一次，当你使用一张单目标卡牌时，你可以令目标相邻的其他角色一并成为该卡牌的目标并摸X张牌，随后你无法使用卡牌指定其他目标。（X为该卡牌指定的角色数量）当所有角色均被你指定过时，修改“汹涌怒火”。
-修改：每回合限一次，当你使用一张单目标卡牌时，你可以令目标相邻的其他任意角色一并成为该卡牌的目标并摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2X张牌，随后你无法使用卡牌指定其他目标。（X为该卡牌指定的角色数量）</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段限一次，你弃置X张牌视为对一名攻击范围内的角色使用X张【杀·物理】，造成伤害后，每以此法造成伤害后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>令目标获得“束缚”并令下一张以此法使用的【杀·物理】伤害+Y。（X为你的已损失血量且至多为5，Y为以此法使用的【杀·物理】造成的伤害次数）</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>你使用卡牌时，可以额外指定场上血量最高的其他角色为目标。你对场上血量最高的其他角色造成伤害时，令该伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>+1。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段限一次，你弃置至多X张牌对攻击范围内一名其他角色造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点伤害，若该角色血量为除你之外全场最高，则令其获得“束缚”。（X为目标已损失血量且至少为1）</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每回合限一次，当场上有【杀】被抵消时，你获得之，你的【闪】视为【杀·物理】，你可以使用更大点数的【杀】抵消其他角色对你使用的【杀】。摸牌阶段你额外摸X张牌，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>出牌阶段你可以额外使用X张【杀】，你的【杀】点数与手牌上限增加X。（X为你的已损失血量且至多为3）</t>
-    </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -1555,22 +1264,6 @@
   </si>
   <si>
     <r>
-      <t>出牌阶段限一次，你可以弃置任意张张红色牌并选择X名已受伤的角色，令其回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量并摸2张牌。（X为你弃置红色牌的数量）</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>当受到过你回复的角色血量发生变化时，你与其各摸</t>
     </r>
     <r>
@@ -1616,53 +1309,1159 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>当前回合结束时，你可以弃置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张手牌令一名本回合受到伤害的角色摸2张牌。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>被动技</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>当你使用伤害类卡牌指向一名角色结算后，你摸1张牌并展示。若展示牌为
+    <r>
+      <t>回合开始时，你可以选择跳过判定阶段、摸牌阶段、出牌阶段和弃牌阶段获得X个“微尘”。回合结束时，你可以分配场上的“微尘”，获得“微尘”的角色回复一点血量。（X为你跳过的阶段数）当你以此法获得的“微尘”数量不小于六</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>时，你修改“过往尘埃”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁定技</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>予愿安洁莉娜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪灵</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>维娜·维多利亚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡兹戴尔</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>遥</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩业星熊</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>水月</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>霍尔海雅</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>山</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>涤火杰西卡</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>寻澜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑕光</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>薇薇安娜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷缪安</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>新约能天使</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>空弦</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑键</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>多萝西</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>娜斯提</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱伊</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>珊比</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐德来希</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔王</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥岩</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻各斯</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>华法琳</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>提丰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒檀</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>死芒</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>焰影苇草</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>白铁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒神</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>怒潮凛冬</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>早露</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>赫拉格</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>锡兰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣聆初雪</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵知</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>忍冬</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>铃兰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>缄默德克萨斯</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒芜拉普兰德</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>林</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>夕</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>海沫</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>引星棘刺</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>絮雨</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝毒</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>教条力场</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>信条</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵营</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能描述1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能描述2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能描述3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>衍生名称1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>衍生描述1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>衍生名称2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>衍生描述2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑恶魔的庇护</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时选择一名角色，令获得“法典”，其摸牌阶段额外摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌，出牌阶段使用【杀】次数+1，手牌上限+1。每回合限一次，当你或其指定对方为目标时，令目标获得1点护甲，摸1张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当拥有“法典”的角色死亡时，你失去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2点血量上限将血量回满，选择其一个技能获得（限定技、觉醒技除外），随后移除“教条力场”获得“信条”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>飘浮大地之上</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段，你可以将手牌摸至体力上限并与一名角色交换座位，随后令双方获得“浮空”并修改“飘浮大地之上”。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你攻击范围内的一名角色受到伤害后血量小于已损失血量，你可以令其获得“浮空”。当你造成或受到伤害后获得“浮空”，你拥有“浮空”时获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>+3攻击范围且使用或打出卡牌后摸1张牌。你失去“浮空”后，弃置场上2张卡牌。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+修改：当你攻击范围内的一名角色受到伤害后血量小于已损失血量，你可以令其获得“浮空”。当你造成或受到伤害后获得“浮空”，你拥有“浮空”时获得+3攻击范围且使用或打出卡牌后摸1张牌。你失去“浮空”后，弃置场上2张卡牌。当其他角色失去“浮空”时，你可以获取其一张卡牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金盟誓</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>准备阶段，你可以弃置至多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张牌并令攻击范围内等量名角色获得“黄金盟誓”（场上至多存在4个“黄金盟誓”）。出牌阶段限一次，你指定一名角色令所有拥有“黄金盟誓”的角色对其使用一张【杀】。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每回合限一次，当你造成伤害时，可以弃置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张手牌视为对相同目标额外造成1点真实伤害。你每回合受到的第一次伤害至多为1。回合开始时，你可以摸1张牌并交给“维娜·维多利亚”1张牌。该卡牌离开宝物栏时销毁。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>进赴故土</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>俱以我之名</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>诸王之息</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻击范围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2，你的【杀】无视对方防具且造成的伤害视为真实伤害。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>凛御银灰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风雪之眼</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法被使用、打出、弃置、移动、销毁，不计入手牌上限，可以被其他角色看到。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你无法随意调整手牌顺序。游戏开始时，将“风雪之眼”置入你的手牌最右侧，位于“风雪之眼”左侧的手牌数值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>+1且不计入手牌上限，使用后你摸2张牌。你造成伤害后令目标获得“寒冷”且可以将1张手牌移动至“风雪之眼”左侧。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>写意胜形</t>
+  </si>
+  <si>
+    <t>工笔入化</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>小自在</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你首次指定一名其他角色或对其造成伤害时，将一个“小自在”置入其宝物区。回合结束时，你摸X张牌。（X为你攻击范围内“小自在”的数量）当一名角色死亡时，若其拥有“小自在”，则本局游戏你造成的伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>+1。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>泼墨淋漓</t>
+  </si>
+  <si>
+    <t>炎</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>老鲤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱凶辟邪</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>小惩大诫</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段，对除你以外任意一名角色使用。将“小惩大诫”置入该角色的判定区内。若判定结果为黑桃，则其获得“束缚”，若判定结果为梅花，则其获得“沉默”。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段，对除你以外任意一名角色使用。将“驱凶辟邪”置入该角色的判定区内。若判定结果为红桃，则其回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量，若判定结果为方片，则其摸2张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>策略技</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>和气生财</t>
+  </si>
+  <si>
+    <t>有备无患</t>
+  </si>
+  <si>
+    <t>当你对一名角色造成伤害后，你可以令其失去X点血量（X为本宝物发动次数且至多为3）。该卡牌离开宝物栏时销毁。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>使用后回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2点血量。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛觉抑制</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>藏品卡牌</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>回合开始时回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗无人机</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你的指向类回复卡牌可以指定其他角色且可以额外指定一个目标。当你为一名角色回复时，随机移除其身上一个负面标记。
+修改：你造成的回复数值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>+1。你的指向类回复卡牌可以指定其他角色且可以额外指定一个目标。当你为一名角色回复时，随机移除其身上一个负面标记。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你造成伤害时令目标获得一个“神经毒素”，拥有“神经毒素”的角色回合结束时，其移除所有“神经毒素”并失去X点血量。每当场上有“神经毒素”被移除时，你摸X张牌。（X为移除“神经毒素”的数量）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>可置入宝物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>可置入藏品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>杂项</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>视为</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>凭空或将一张牌当作某一张牌使用或打出</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>损伤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣山的祝福</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜涛覆岭</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>古朴的急救箱</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，你获得“屏障”。当你失去屏障时，你可以视为对攻击范围内任意名角色使用一张【杀】，若此【杀】造成伤害，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌。回合开始或回合结束时，若你没有“屏障”，则可以弃置2张手牌获得“屏障”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你造成血量回复时摸1张牌，若目标角色拥有负面标记则随机移除1个并摸1张牌。出牌阶段限一次，你展示一名其他角色的一张手牌并获得，若为红色，则令该角色回复1点血量且此技能视为未发动过，若为黑色，则你令其下次受到伤害后摸2张牌。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>限定技</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>火山回响</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对攻击范围内的一名角色使用。获取其</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张手牌并进行三次判定，当判定结果为黑色时获得“寒冷”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有角色使用。目标角色需要依次打出一张【闪】，否则该角色受到一点法术伤害。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>对你自己使用，抽取三张卡牌，弃置其中一张。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对所有角色使用，令所有角色回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量并移除1个负面标记。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备阶段，将【兰登战术】置入你的武器栏。出牌阶段限一次，你可以弃置至多X张【杀】视为使用X张不计入次数的【杀·物理】，以此法转化的【杀·物理】造成伤害后，你摸1张牌。（X为你的当前血量）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏开始时，将投递坐标置入你的宝物栏。准备阶段，若场上有“投递坐标”则你可以将其移动，若场上没有，则将其置入你的宝物栏。持有“投递坐标”的角色进入濒死状态时，你可以将其拥有的“投递坐标”移出游戏并将其血量回复至其中“快递”数量。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段限一次，你可以失去至多3个自己的“弹药”，并选择X个攻击范围内的角色对其造成1点物理伤害（X为“弹药”失去数量）。当你造成伤害时，你可以失去1个自己的“弹药”令此次伤害+1。弃牌阶段结束时，你可以弃置任意张【杀】并获得等量“弹药”。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合限一次，当你使用或打出一张牌后，可以从牌堆底摸一张牌展示并交给场上任意一名角色，若展示牌与使用牌类型相同，此技能视为未发动过。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前角色回合结束时，若你的血量与手牌数均未发生变动，则你可以摸X张牌并将X张牌以任意顺序放回牌堆底。（X为你的血量上限）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，你获得“屏障”。当场上有“屏障”触发时，你与其各摸1张牌并令其视为对攻击范围内至多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2名角色使用一张【杀·法术】。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段限，你可以弃置X张手牌并选择一名角色，令其获得“屏障”，以此法获得的“屏障”失效后，其回复1点血量并获得“庇护”。（X为目标当前血量除以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2向下取整且至少为1）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段，你令下一张指向性单一目标卡牌不计次数限制且额外选择至多两个目标，该卡牌造成伤害时令对应目标获得“晕眩”，在该卡牌结算后你流失X点体力。（X为该卡牌选择目标数减去造成伤害数）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你使用单目标指向性卡牌可以额外指定一名角色，若该卡牌仅指定一名目标，则在造成伤害后令其获得“浮空”。当一名角色获得“浮空”后，你可以对其造成X点伤害并摸X张牌。（X为你与其距离-1且至多为3。）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，将【机动盾牌】置入你的宝物区。回合开始时，你可以弃置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张手牌将【机动盾牌】置入你的宝物区，若你的宝物区有【机动盾牌】，则获得1点护甲。当你的护甲减少时，抽一张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>准备阶段，你可以摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张牌并选择其中一个策略触发：
+①：本回合攻击范围+1且你使用的【杀】伤害+1
+②：可以额外使用一张【杀】且【杀】可以额外指定一名目标
+③：本回合你无法使用伤害类卡牌，你可以将2张【杀】视为“坚守阵线”使用。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>使用后获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2点护甲。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚守阵线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段开始时，你可以令本回合内你的所有回复卡牌被视为【杀·物理】或【杀·法术】使用或打出，以此法使用的卡牌无次数限制且造成的伤害+1，若造成伤害则选择一名其他角色回复等量生命值。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的手牌上限等于血量上限，摸牌阶段开始时，你放弃摸牌并将手牌补充至血量上限。当一名角色的卡牌进入弃牌堆时，你可以弃置一张相同类型的卡牌获得（以此法获得的卡牌无次数与距离限制）。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你的攻击范围始终为2。当场上有“灼燃损伤”触发时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌并可以令其下一回合的出【杀】次数-1。
+修改：你的攻击范围始终为3。当场上有“灼燃损伤”触发时，你摸1张牌并可以令其下一回合的出【杀】次数-1且对其造成2点真实伤害。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每名角色的回合结束时，若场上角色均受到过伤害，则你指定任意名角色回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量，随后令一名角色立刻执行一个额外回合，该回合内每当有角色的血量发生变化时，你与该角色各摸1张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对除你以外任意一名角色使用。将“旧日残影”置入该角色的判定区内，其需弃置一张与判定结果相同花色的手牌，若没有弃置则对其造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点凋亡伤害。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟卡牌</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>使用后你失去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量，令本回合你下一次造成的伤害翻倍。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段，对你使用，将“正霆摄威”置于你的判定区里，若当判定结果为梅花</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1~7，则对目标角色造成1点法术伤害并移动到下家的判定区内，若判定结果为黑桃2~9，则对目标角色造成3点法术伤害，若均不为以上结果，则将其移动到下家的判定区内。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>正霆摄威</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，你获得“屏障”，当你失去屏障时，回复1点血量并摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张牌。每回合结束时，若你本回合没有受到伤害，则你可以弃置2张手牌获得“屏障”。你的“屏障”拥有上限为3。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段，你失去一个“屏障”并令下一张使用的卡牌指定攻击范围内的所有角色且不可响应，若该卡牌造成伤害，则令目标获得“眩晕”。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你造成伤害时，你令目标获得“寒冷”，当场上拥有“寒冷”的角色受到伤害时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌，当场上有角色获得“冻结”时候，你摸2张牌。你无法获得“冻结”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>准备阶段，将【悲叹的仆役】置入你的宝物栏，你拥有【悲叹的仆役】时其他角色距离你+1。当你对其他角色造成伤害时，你将【悲叹的仆役】置入其宝物栏并可以获取其一张卡牌（每回合每名角色限制一次）拥有【悲叹的仆役】的角色无法指定你为目标，且其造成或受到伤害时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前回合结束时，若你本回合造成过伤害，则你可以选择一名其他角色，令你与其各视为使用一张【杀·法术】，若该【杀·法术】令一名角色进入濒死，则你视为使用一张【杀·法术】。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，你将3个【白铁™多功能平台】置入场上角色的宝物栏。（每名角色至多获得一个【白铁™多功能平台】）当【白铁™多功能平台】销毁时，你摸X张牌。（X为【白铁™多功能平台】升级次数）回合开始时，你可以弃置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张手牌将【白铁™多功能平台】置入一名角色的宝物栏。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你令所有拥有“迷狂牢笼”的角色打出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张【杀】，若有角色拒绝，则你对其造成1点法术伤害。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，将“诸王之息”置入你的武器栏，当你持有“诸王之息”时，你的【杀】可以额外指定一名角色，当场上有角色造成真实伤时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌。出牌阶段限一次，你可以弃置1张手牌获得“诸王之息”，无论它在哪。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段限一次，你弃置X张牌视为对一名攻击范围内的角色使用X张【杀·物理】，造成伤害后，每以此法造成伤害后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>令目标获得“束缚”并令下一张以此法使用的【杀·物理】伤害+Y。（X为你的已损失血量且至多为3，Y为以此法使用的【杀·物理】造成的伤害次数）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你使用卡牌时，可以额外指定场上血量最高的其他角色为目标。你对场上血量最高的其他角色造成伤害时，令该伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>+1。当场上有其他角色获得“束缚”时，你摸1张牌并视为对其使用一张【杀·物理】。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段限一次，你弃置至多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>3张牌视为对攻击范围内等量名其他角色使用一张【杀·物理】，若此【杀】造成伤害且该角色血量为除你之外全场最高，则令其获得“束缚”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你造成伤害时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌并弃置1张牌令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你造成伤害时，你令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。你对“冻结”角色造成的伤害+1且每回合首次指定其为目标的卡牌额外结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2次。你无法获得“冻结”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每回合限一次，当你使用卡牌指定其他角色为目标时，你可以摸X张牌并可以将“风雪之眼”左右两侧的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌交换，若有角色获得“冻结”则本技能视为未发动过。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（X为该卡牌指定的目标数）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你使用伤害类卡牌指向一名角色时，你摸1张牌并展示。若展示牌为
 ①红色：则你获得“迷彩”。
 ②黑色：则你视为使用一张【杀·物理】（该【杀】无法触发“隐狐之艺”且不计入次数限制）。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>回合开始时，你可以选择跳过判定阶段、摸牌阶段、出牌阶段和弃牌阶段获得X个“微尘”。回合结束时，你可以分配场上的“微尘”，获得“微尘”的角色回复一点血量。（X为你跳过的阶段数）当你以此法获得的“微尘”数量不小于六</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>时，你修改“过往尘埃”。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>锁定技</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>游戏开始时，你获得</t>
     </r>
     <r>
@@ -1673,518 +2472,56 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>1个“浩劫”，你指定拥有“浩劫”的角色时，令其获得“沉默”。出牌阶段，你可以移动一个“浩劫”并获得目标1张手牌。拥有“浩劫”的其他角色回合开始时，其进行判定，若结果为：
+      <t>1个“浩劫”，你指定拥有“浩劫”的其他角色时，令其获得“沉默”。出牌阶段，你可以移动一个“浩劫”并获得目标1张手牌（每名角色至多拥有1个“浩劫”）。拥有“浩劫”的其他角色回合开始时，其进行判定，若结果为：
 ①黑色：其流失1点血量。若其因此进入濒死，你将手牌补充至体力上限。
-②红色：你对其视为使用1张【杀·法术】，若其因此进入濒死，你获得其所有红色牌。
+②红色：你对其视为使用1张【杀·法术】，若其因此进入濒死，你获得其所有黑色牌。
 随后移除“浩劫”。</t>
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>当一名角色的出牌阶段结束时，若其在本阶段内未造成伤害，你可以弃置一张手牌视为对其使用1张【杀·法术】。你跳过摸牌阶段与弃牌阶段，当有角色的阶段被跳过时，你摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌并获得1个“浩劫”。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>予愿安洁莉娜</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪灵</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>维娜·维多利亚</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>卡兹戴尔</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>名称</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>遥</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩业星熊</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>水月</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>霍尔海雅</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>山</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>涤火杰西卡</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>寻澜</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>瑕光</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>薇薇安娜</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷缪安</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>新约能天使</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>空弦</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯烬艾雅法拉</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑键</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>多萝西</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>娜斯提</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱伊</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>珊比</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐德来希</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔王</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>泥岩</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>逻各斯</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>华法琳</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>提丰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒檀</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>死芒</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>焰影苇草</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>白铁</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>酒神</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>怒潮凛冬</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>早露</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>赫拉格</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>锡兰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣聆初雪</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵知</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>忍冬</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>铃兰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>缄默德克萨斯</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒芜拉普兰德</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>林</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>夕</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>海沫</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>引星棘刺</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>絮雨</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝毒</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>教条力场</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>信条</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>阵营</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能描述1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能描述2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能描述3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生名称1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生描述1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生名称2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生描述2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑恶魔的庇护</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>y</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的手牌上限等于血量上限，摸牌阶段开始时，你放弃摸牌并将手牌补充至血量上限，当一名角色的卡牌进入弃牌堆时，你可以弃置一张相同类型的卡牌获得。（以此技能获得的卡牌无次数限制）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>游戏开始时选择一名角色，令获得“法典”，其摸牌阶段额外摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌，出牌阶段使用【杀】次数+1，手牌上限+1。每回合限一次，当你或其指定对方为目标时，令目标获得1点护甲，摸1张牌。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当拥有“法典”的角色死亡时，你失去</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2点血量上限将血量回满，选择其一个技能获得（限定技、觉醒技除外），随后移除“教条力场”获得“信条”。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>飘浮大地之上</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段，你可以将手牌摸至体力上限并与一名角色交换座位，随后令双方获得“浮空”并修改“飘浮大地之上”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当你攻击范围内的一名角色受到伤害后血量小于已损失血量，你可以令其获得“浮空”。当你造成或受到伤害后获得“浮空”，你拥有“浮空”时获得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>+3攻击范围且使用或打出卡牌后摸1张牌。你失去“浮空”后，弃置场上2张卡牌。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-修改：当你攻击范围内的一名角色受到伤害后血量小于已损失血量，你可以令其获得“浮空”。当你造成或受到伤害后获得“浮空”，你拥有“浮空”时获得+3攻击范围且使用或打出卡牌后摸1张牌。你失去“浮空”后，弃置场上2张卡牌。当其他角色失去“浮空”时，你可以获取其一张卡牌。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄金盟誓</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>准备阶段，你可以弃置至多</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2张牌并令攻击范围内等量名角色获得“黄金盟誓”（场上至多存在4个“黄金盟誓”）。出牌阶段限一次，你指定一名角色令所有拥有“黄金盟誓”的角色对其使用一张【杀】。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每回合限一次，当你造成伤害时，可以弃置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张手牌视为对相同目标额外造成1点真实伤害。你每回合受到的第一次伤害至多为1。回合开始时，你可以摸1张牌并交给“维娜·维多利亚”1张牌。该卡牌离开宝物栏时销毁。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>进赴故土</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>俱以我之名</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>诸王之息</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>攻击范围</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2，你的【杀】无视对方防具且造成的伤害视为真实伤害。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>游戏开始时，将“诸王之息”置入你的武器栏，当你持有“诸王之息”时，你的【杀】可以额外指定一名角色且当场上有角色造成真实伤时，你摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌。出牌阶段限一次，你可以弃置2张手牌获得“诸王之息”，无论它在哪。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>凛御银灰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>风雪之眼</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法被使用、打出、弃置、移动、销毁，不计入手牌上限，可以被其他角色看到。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>你无法随意调整手牌顺序。游戏开始时，将“风雪之眼”置入你的手牌最右侧，位于“风雪之眼”左侧的手牌数值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>+1且不计入手牌上限，使用后你摸2张牌。你造成伤害后令目标获得“寒冷”且可以将1张手牌移动至“风雪之眼”左侧。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段，你可以弃置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张手牌销毁“小自在”。该卡牌离开宝物栏时销毁。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>写意胜形</t>
-  </si>
-  <si>
-    <t>工笔入化</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>小自在</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>视为使用或打出任意一张非装备牌（每回合每种牌名限一次）。进入弃牌堆时销毁。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>游戏开始时，将“工笔入化”置入你的手牌。出牌阶段，你可以弃置</t>
+      <t>当前回合结束时，若有角色受到过伤害，则你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>可以弃置1张手牌令一名本回合受到伤害的角色摸2张牌，当弃置的卡牌为伤害类卡牌，改为摸3张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你始终跳过摸牌阶段与弃牌阶段，当有角色的阶段被跳过时，你摸1张牌并获得1个“浩劫”。一名角色的回合结束时，若其在本阶段内未弃置卡牌，则你可以弃置一张手牌视为对其使用1张【杀·法术】。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段限一次，你可以弃置至多X张牌并失去“屏障”，令攻击范围内的等量名角色获得“晕眩”。（X为你的攻击范围）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你使用卡牌指定“夕”为目标时，令其摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌。出牌阶段，你可以弃置1张手牌销毁“小自在”。该卡牌离开宝物栏时销毁。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>首轮或准备阶段开始时，将“工笔入化”置入你的手牌。出牌阶段，你可以弃置</t>
     </r>
     <r>
       <rPr>
@@ -2199,118 +2536,11 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>你首次指定一名其他角色或对其造成伤害时，将一个“小自在”置入其宝物区。回合结束时，你摸X张牌。（X为你攻击范围内“小自在”的数量）当一名角色死亡时，若其拥有“小自在”，则本局游戏你造成的伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>+1。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>泼墨淋漓</t>
-  </si>
-  <si>
-    <t>炎</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>老鲤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>每回合限一次，当你使用卡牌指定其他角色为目标时，你可以摸X张牌并可以将“风雪之眼”左右两侧的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌交换，若该卡牌造成伤害则本技能视为未发动过。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（X为该卡牌指定的目标数）</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱凶辟邪</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>小惩大诫</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段，对除你以外任意一名角色使用。将“小惩大诫”置入该角色的判定区内。若判定结果为黑桃，则其获得“束缚”，若判定结果为梅花，则其获得“沉默”。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段，对除你以外任意一名角色使用。将“驱凶辟邪”置入该角色的判定区内。若判定结果为红桃，则其回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量，若判定结果为方片，则其摸2张牌。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>策略技</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>和气生财</t>
-  </si>
-  <si>
-    <t>有备无患</t>
-  </si>
-  <si>
-    <t>游戏开始时你的手牌获得“符箓”标记。当有角色的判定牌生效时，你从牌堆中展示与判定牌点数、花色、类型的卡牌各一张，随后选择其中一张代替判定牌，获取一牌并标记为“符箓”，将一张牌置于牌堆顶。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当你攻击范围内有其他角色进入濒死时，你回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量，若由你致其濒死，则额外摸3张牌。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>准备阶段，出牌阶段结束时，你可以将一张牌当作你上一张使用过的伤害类牌使用。（不计入次数限制）</t>
+    <t>视为使用或打出任意一张非装备牌（所有“工笔入化”每回合每种牌名限一次）。进入弃牌堆时销毁。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段，你可以将拥有“符箓”标记的卡牌视为“驱凶辟邪”或“小惩大诫”对一名角色使用。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -2325,8 +2555,31 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>/回复血量/受到伤害后，你摸等量牌/回复等量血量/受到等量伤害。</t>
-    </r>
+      <t>/弃牌/回复血量/受到伤害后，你摸等量牌/弃置等量牌/回复等量血量/受到等量伤害。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段，你可以选择其中一个策略触发并移除：
+①：你可以令一名攻击范围内的角色获得“沉默”并视为对其使用1张不计次数的【杀·法术】。
+②：你可以令一名攻击范围内的角色下一次受到的法术伤害+1，并视为对其使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张不计次数的【杀·法术】。
+③：你可以令X名攻击范围内的角色获得“晕眩”，并视为对其中至多3个目标视为使用1张不计次数的【杀·法术】。（X为你的攻击范围）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>本局游戏限一次，当你杀死一名角色时，你获得其所有卡牌并将“蓝莓与黑巧”重置为游戏开始时的状态。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -2345,100 +2598,59 @@
       </rPr>
       <t xml:space="preserve">
 ③：令拥有“炼金单元”角色攻击范围内的X名角色获得“禁疗”并对其造成1点法术伤害。
-（X为弃置手牌数量除以2向下取整）</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你对一名角色造成伤害后，你可以令其失去X点血量（X为本宝物发动次数且至多为3）。该卡牌离开宝物栏时销毁。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>使用后回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2点血量。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>痛觉抑制</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>藏品卡牌</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>回合开始时回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>医疗无人机</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段每项限一次，你可以将拥有“符箓”标记的卡牌视为：
-①：“驱凶辟邪”对其他角色使用。
-②：“小惩大诫”对其他角色使用。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段限一次，你弃置一张红色牌并选择攻击范围内的一名角色，若其在当前回合没有受到伤害，则回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量，持续至你的下回合结束。当你以此法回复不小于3点血量时，修改“痛觉抑制”。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>你的指向类回复卡牌可以指定其他角色且可以额外指定一个目标。当你为一名角色回复时，随机移除其身上一个负面标记。
-修改：你造成的回复数值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>+1。你的指向类回复卡牌可以指定其他角色且可以额外指定一个目标。当你为一名角色回复时，随机移除其身上一个负面标记。</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>你【杀】可以额外指定一名角色，每当你使用</t>
+（X为弃置手牌数量除以2向下取整且至少为1）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你攻击范围内有其他角色进入濒死时，你回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量，若由你致其濒死，则额外摸3张牌。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每回合限一次，你使用或打出的第一张手牌在结算后收回手牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备阶段，出牌阶段结束时，你可以将一张手牌视为一张单目标伤害类牌使用（不计入次数限制）。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段限一次，你弃置一张红色牌并选择攻击范围内的一名角色，若其在当前回合没有受到伤害，则其回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量，反之，你摸1张牌，持续至你的下回合开始，每轮限一次，当其进入濒死时，你从牌堆中抽取一张单目标回复卡牌。当你以此法回复不小于3点血量时，修改“痛觉抑制”。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你【杀】可以视为任意【杀·损伤】使用且可以额外指定一名角色，每当你使用</t>
     </r>
     <r>
       <rPr>
@@ -2453,59 +2665,90 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>当你造成伤害时令目标获得一个“神经毒素”，拥有“神经毒素”的角色回合结束时，其移除所有“神经毒素”并失去X点血量。每当场上有“神经毒素”被移除时，你摸X张牌。（X为移除“神经毒素”的数量）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>可置入宝物</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>可置入藏品</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>杂项</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>视为</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>凭空或将一张牌当作某一张牌使用或打出</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>损伤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣山的祝福</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>霜涛覆岭</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>古朴的急救箱</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合</t>
+    <r>
+      <t>首轮开始时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张卡牌并标记为“符箓”。当有角色的判定牌生效时，你从牌堆中展示与判定牌点数、花色、类型的卡牌各一张，随后选择其中一张代替判定牌，获取其余卡牌并选择一张标记为“符箓”。每回合每名角色限一次，你使用卡牌指定判定区内有牌的角色时，选择一项执行：
+①：令该卡牌对其额外结算一次。
+②：摸2张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段限一次，你可以弃置任意张红色牌并选择X名角色，令其回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量并摸X张牌。（X为你弃置红色牌的数量）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当场上有【杀】被抵消时，你可以摸1张牌并失去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量获得之，你的【闪】视为【杀·物理】，你可以使用更大点数的【杀】抵消其他角色对你使用的【杀】。摸牌阶段你额外摸X张牌，出牌阶段你可以额外使用X张【杀】，你的【杀】点数与手牌上限增加X。（X为你的已损失血量）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每回合限一次，当你使用一张单目标卡牌时，你可以令目标相邻的其他角色一并成为该卡牌的目标并摸X张牌，随后本回合内你无法使用卡牌指定其他不以此卡牌指定的目标。（X为该卡牌指定的角色数量）当所有角色均被你指定过时，修改“汹涌怒火”。
+修改：每回合限一次，当你使用一张单目标卡牌时，你可以令目标相邻的其他任意角色一并成为该卡牌的目标并摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2X张牌，随后本回合内你无法使用卡牌指定其他不以此卡牌指定的角色目标。（X为该卡牌指定的角色数量）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段，对所有角色使用。你从牌堆顶亮出等同于现存角色数量的牌，然后按行动顺序结算，目标角色选择并获得其中的一张，因此获得红色牌的角色回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量，获得黑色牌的角色摸1张牌。</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>百谷长青</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2695,7 +2938,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2822,13 +3065,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2844,7 +3081,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2856,14 +3099,23 @@
     <xf numFmtId="49" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3160,7 +3412,7 @@
     <col min="10" max="10" width="16.5" style="6" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="8" customWidth="1"/>
     <col min="12" max="12" width="116.375" style="10" customWidth="1"/>
-    <col min="13" max="13" width="26.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="40.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="17.625" style="7" customWidth="1"/>
     <col min="15" max="15" width="102.375" style="15" customWidth="1"/>
     <col min="16" max="16" width="42.125" style="3" customWidth="1"/>
@@ -3175,55 +3427,55 @@
   <sheetData>
     <row r="1" spans="1:18" s="33" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="G1" s="33" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="J1" s="33" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="K1" s="33" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="L1" s="33" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
       <c r="M1" s="33" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="N1" s="33" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="O1" s="33" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="P1" s="33" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="R1" s="33" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3231,24 +3483,24 @@
         <v>16</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D2" s="26"/>
       <c r="E2" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>71</v>
+      <c r="F2" s="57" t="s">
+        <v>359</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="18" t="s">
-        <v>94</v>
+      <c r="I2" s="57" t="s">
+        <v>360</v>
       </c>
       <c r="J2" s="26"/>
       <c r="K2" s="19"/>
@@ -3264,24 +3516,24 @@
         <v>16</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="G3" s="26"/>
       <c r="H3" s="16" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="J3" s="26"/>
       <c r="K3" s="16"/>
@@ -3297,24 +3549,24 @@
         <v>16</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="16" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="G4" s="26"/>
       <c r="H4" s="16" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>117</v>
+        <v>361</v>
       </c>
       <c r="J4" s="26"/>
       <c r="K4" s="16"/>
@@ -3330,24 +3582,24 @@
         <v>12</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D5" s="26"/>
       <c r="E5" s="16" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>128</v>
+        <v>362</v>
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="16"/>
@@ -3363,17 +3615,17 @@
         <v>12</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="16" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="16"/>
@@ -3392,24 +3644,24 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>109</v>
+        <v>75</v>
+      </c>
+      <c r="F7" s="57" t="s">
+        <v>363</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>86</v>
+      <c r="I7" s="57" t="s">
+        <v>364</v>
       </c>
       <c r="J7" s="26"/>
       <c r="K7" s="16"/>
@@ -3418,10 +3670,10 @@
         <v>18</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O7" s="21" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="P7" s="22"/>
       <c r="R7" s="11"/>
@@ -3431,24 +3683,24 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>112</v>
+        <v>357</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>141</v>
+        <v>358</v>
       </c>
       <c r="J8" s="26"/>
       <c r="K8" s="16"/>
@@ -3464,24 +3716,24 @@
         <v>9</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>52</v>
+        <v>367</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="19" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J9" s="26"/>
       <c r="K9" s="24"/>
@@ -3497,35 +3749,35 @@
         <v>9</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>59</v>
+        <v>75</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>369</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J10" s="26"/>
       <c r="K10" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="16"/>
@@ -3535,43 +3787,43 @@
     </row>
     <row r="11" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="26" t="s">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="P11" s="41" t="s">
-        <v>337</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3579,24 +3831,24 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>88</v>
+        <v>356</v>
       </c>
       <c r="J12" s="26"/>
       <c r="K12" s="16"/>
@@ -3612,33 +3864,33 @@
         <v>6</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>284</v>
+        <v>241</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>72</v>
+        <v>355</v>
       </c>
       <c r="M13" s="26"/>
       <c r="N13" s="16"/>
@@ -3651,24 +3903,24 @@
         <v>6</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="16" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>130</v>
+        <v>354</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="16"/>
@@ -3684,24 +3936,24 @@
         <v>10</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>131</v>
+        <v>347</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>132</v>
+        <v>348</v>
+      </c>
+      <c r="I15" s="57" t="s">
+        <v>370</v>
       </c>
       <c r="J15" s="26"/>
       <c r="K15" s="16"/>
@@ -3717,24 +3969,24 @@
         <v>10</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="16" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="I16" s="27" t="s">
-        <v>151</v>
+        <v>120</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>129</v>
       </c>
       <c r="J16" s="26"/>
       <c r="K16" s="16"/>
@@ -3750,24 +4002,24 @@
         <v>5</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D17" s="26"/>
       <c r="E17" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="16" t="s">
         <v>51</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J17" s="26"/>
       <c r="K17" s="16"/>
@@ -3783,19 +4035,19 @@
         <v>5</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>289</v>
+        <v>246</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="16"/>
@@ -3804,22 +4056,22 @@
       <c r="K18" s="16"/>
       <c r="L18" s="18"/>
       <c r="M18" s="26" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="O18" s="27" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="P18" s="26" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3827,30 +4079,30 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="16" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="27" t="s">
-        <v>164</v>
+        <v>140</v>
+      </c>
+      <c r="I19" s="57" t="s">
+        <v>141</v>
       </c>
       <c r="J19" s="26"/>
       <c r="K19" s="16"/>
       <c r="L19" s="18"/>
       <c r="M19" s="26" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N19" s="16"/>
       <c r="O19" s="21"/>
@@ -3862,24 +4114,24 @@
         <v>15</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="27" t="s">
         <v>143</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>166</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="16" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="J20" s="26"/>
       <c r="K20" s="16"/>
@@ -3895,36 +4147,36 @@
         <v>2</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G21" s="26"/>
       <c r="H21" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J21" s="26"/>
       <c r="K21" s="16"/>
       <c r="L21" s="25"/>
       <c r="M21" s="26" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N21" s="16" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P21" s="22"/>
       <c r="R21" s="11"/>
@@ -3934,26 +4186,26 @@
         <v>2</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="J22" s="26"/>
       <c r="K22" s="16"/>
@@ -3969,24 +4221,24 @@
         <v>2</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>98</v>
+        <v>75</v>
+      </c>
+      <c r="F23" s="57" t="s">
+        <v>376</v>
       </c>
       <c r="G23" s="26"/>
       <c r="H23" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>159</v>
+        <v>377</v>
       </c>
       <c r="J23" s="26"/>
       <c r="K23" s="16"/>
@@ -4002,28 +4254,28 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="I24" s="27" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="J24" s="26"/>
       <c r="K24" s="16"/>
@@ -4039,26 +4291,26 @@
         <v>2</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="16" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I25" s="27" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="J25" s="26"/>
       <c r="K25" s="16"/>
@@ -4074,25 +4326,25 @@
         <v>2</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I26" s="40" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4100,28 +4352,28 @@
         <v>46</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="J27" s="26"/>
       <c r="K27" s="16"/>
@@ -4137,24 +4389,24 @@
         <v>46</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>298</v>
+        <v>255</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="27" t="s">
-        <v>204</v>
+      <c r="F28" s="57" t="s">
+        <v>378</v>
       </c>
       <c r="G28" s="33"/>
       <c r="H28" s="16" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="I28" s="27" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="J28" s="26"/>
       <c r="K28" s="16"/>
@@ -4170,46 +4422,46 @@
         <v>1</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="27" t="s">
-        <v>200</v>
+        <v>75</v>
+      </c>
+      <c r="F29" s="57" t="s">
+        <v>379</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="M29" s="26" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="P29" s="22"/>
       <c r="R29" s="11"/>
@@ -4219,28 +4471,28 @@
         <v>1</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>207</v>
+        <v>380</v>
       </c>
       <c r="J30" s="23"/>
       <c r="K30" s="16"/>
@@ -4256,24 +4508,24 @@
         <v>7</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>133</v>
+        <v>75</v>
+      </c>
+      <c r="F31" s="57" t="s">
+        <v>381</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="J31" s="26"/>
       <c r="K31" s="16"/>
@@ -4282,10 +4534,10 @@
         <v>21</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="P31" s="22"/>
       <c r="R31" s="11"/>
@@ -4295,55 +4547,55 @@
         <v>7</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E32" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32" s="57" t="s">
+        <v>382</v>
+      </c>
+      <c r="J32" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="F32" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32" s="35" t="s">
+      <c r="K32" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="L32" s="27" t="s">
         <v>163</v>
-      </c>
-      <c r="I32" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="K32" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="L32" s="27" t="s">
-        <v>191</v>
       </c>
       <c r="M32" s="26" t="s">
         <v>22</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="O32" s="29" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="P32" s="26" t="s">
         <v>23</v>
       </c>
       <c r="Q32" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="R32" s="28" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
@@ -4351,37 +4603,37 @@
         <v>7</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>351</v>
+        <v>221</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>383</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="H33" s="35" t="s">
         <v>49</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O33" s="42" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4389,26 +4641,26 @@
         <v>13</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>303</v>
+        <v>260</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>251</v>
+        <v>215</v>
+      </c>
+      <c r="F34" s="57" t="s">
+        <v>410</v>
       </c>
       <c r="G34" s="26"/>
       <c r="H34" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>252</v>
+        <v>216</v>
+      </c>
+      <c r="I34" s="57" t="s">
+        <v>384</v>
       </c>
       <c r="J34" s="26"/>
       <c r="K34" s="16"/>
@@ -4424,24 +4676,24 @@
         <v>13</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>253</v>
+        <v>215</v>
+      </c>
+      <c r="F35" s="57" t="s">
+        <v>385</v>
       </c>
       <c r="G35" s="26"/>
       <c r="H35" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>254</v>
+        <v>216</v>
+      </c>
+      <c r="I35" s="57" t="s">
+        <v>386</v>
       </c>
       <c r="J35" s="26"/>
       <c r="K35" s="16"/>
@@ -4457,17 +4709,17 @@
         <v>13</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>255</v>
+        <v>214</v>
+      </c>
+      <c r="F36" s="57" t="s">
+        <v>409</v>
       </c>
       <c r="G36" s="26"/>
       <c r="H36" s="16"/>
@@ -4486,24 +4738,24 @@
         <v>17</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="16" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
       <c r="G37" s="26"/>
       <c r="H37" s="16" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="J37" s="26"/>
       <c r="K37" s="16"/>
@@ -4519,24 +4771,24 @@
         <v>17</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="14" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="G38" s="26"/>
       <c r="H38" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>258</v>
+        <v>216</v>
+      </c>
+      <c r="I38" s="57" t="s">
+        <v>408</v>
       </c>
       <c r="J38" s="26"/>
       <c r="K38" s="16"/>
@@ -4552,31 +4804,31 @@
         <v>8</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F39" s="18" t="s">
-        <v>178</v>
+      <c r="F39" s="57" t="s">
+        <v>387</v>
       </c>
       <c r="G39" s="26"/>
       <c r="H39" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J39" s="26"/>
       <c r="K39" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="M39" s="26"/>
       <c r="N39" s="16"/>
@@ -4589,24 +4841,24 @@
         <v>8</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="18" t="s">
-        <v>179</v>
+      <c r="F40" s="57" t="s">
+        <v>388</v>
       </c>
       <c r="G40" s="26"/>
       <c r="H40" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="J40" s="26"/>
       <c r="K40" s="16"/>
@@ -4622,31 +4874,31 @@
         <v>8</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41" s="40" t="s">
-        <v>366</v>
+        <v>75</v>
+      </c>
+      <c r="I41" s="60" t="s">
+        <v>389</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O41" s="15" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4654,26 +4906,26 @@
         <v>11</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D42" s="26"/>
       <c r="E42" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>264</v>
+        <v>390</v>
       </c>
       <c r="J42" s="26"/>
       <c r="K42" s="16"/>
@@ -4689,24 +4941,24 @@
         <v>11</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D43" s="26"/>
       <c r="E43" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>262</v>
+        <v>75</v>
+      </c>
+      <c r="F43" s="57" t="s">
+        <v>392</v>
       </c>
       <c r="G43" s="26"/>
       <c r="H43" s="16" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="I43" s="39" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="J43" s="26"/>
       <c r="K43" s="16"/>
@@ -4722,28 +4974,28 @@
         <v>11</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>203</v>
+        <v>401</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I44" s="18" t="s">
-        <v>108</v>
+      <c r="I44" s="57" t="s">
+        <v>400</v>
       </c>
       <c r="J44" s="26"/>
       <c r="K44" s="16"/>
@@ -4759,24 +5011,24 @@
         <v>11</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>267</v>
+        <v>221</v>
+      </c>
+      <c r="F45" s="57" t="s">
+        <v>391</v>
       </c>
       <c r="G45" s="26"/>
       <c r="H45" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="I45" s="39" t="s">
-        <v>268</v>
+        <v>225</v>
+      </c>
+      <c r="I45" s="57" t="s">
+        <v>393</v>
       </c>
       <c r="J45" s="26"/>
       <c r="K45" s="16"/>
@@ -4792,24 +5044,24 @@
         <v>3</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46" s="18" t="s">
-        <v>138</v>
+        <v>75</v>
+      </c>
+      <c r="F46" s="57" t="s">
+        <v>346</v>
       </c>
       <c r="G46" s="26"/>
       <c r="H46" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>106</v>
+        <v>394</v>
       </c>
       <c r="J46" s="26"/>
       <c r="K46" s="16"/>
@@ -4825,77 +5077,77 @@
         <v>3</v>
       </c>
       <c r="B47" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="C47" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>363</v>
-      </c>
       <c r="E47" s="16" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="I47" s="39" t="s">
-        <v>361</v>
+        <v>221</v>
+      </c>
+      <c r="I47" s="57" t="s">
+        <v>396</v>
       </c>
       <c r="K47" s="16"/>
       <c r="L47" s="39"/>
       <c r="M47" s="26" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="N47" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="O47" s="43" t="s">
-        <v>356</v>
+        <v>72</v>
+      </c>
+      <c r="O47" s="61" t="s">
+        <v>395</v>
       </c>
       <c r="P47" s="26" t="s">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="Q47" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="R47" s="44" t="s">
-        <v>360</v>
+        <v>71</v>
+      </c>
+      <c r="R47" s="58" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="26" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>374</v>
+        <v>225</v>
+      </c>
+      <c r="F48" s="60" t="s">
+        <v>407</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>373</v>
+        <v>324</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="I48" s="40" t="s">
-        <v>385</v>
+        <v>49</v>
+      </c>
+      <c r="I48" s="60" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4903,24 +5155,24 @@
         <v>14</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D49" s="26"/>
       <c r="E49" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="F49" s="39" t="s">
-        <v>375</v>
+        <v>223</v>
+      </c>
+      <c r="F49" s="57" t="s">
+        <v>403</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="16" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="J49" s="26"/>
       <c r="K49" s="16"/>
@@ -4933,36 +5185,36 @@
         <v>14</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D50" s="26"/>
       <c r="E50" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="F50" s="39" t="s">
-        <v>377</v>
+        <v>223</v>
+      </c>
+      <c r="F50" s="57" t="s">
+        <v>399</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="I50" s="39" t="s">
-        <v>378</v>
+        <v>322</v>
+      </c>
+      <c r="I50" s="57" t="s">
+        <v>402</v>
       </c>
       <c r="J50" s="26"/>
       <c r="K50" s="16"/>
       <c r="L50" s="18"/>
       <c r="M50" s="26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N50" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O50" s="43" t="s">
-        <v>379</v>
+        <v>325</v>
       </c>
       <c r="P50" s="22"/>
       <c r="R50" s="11"/>
@@ -4972,26 +5224,26 @@
         <v>14</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="F51" s="39" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="I51" s="39" t="s">
-        <v>386</v>
+        <v>221</v>
+      </c>
+      <c r="I51" s="57" t="s">
+        <v>405</v>
       </c>
       <c r="J51" s="26"/>
       <c r="K51" s="16"/>
@@ -5007,24 +5259,24 @@
         <v>14</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>319</v>
+        <v>276</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="16" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="I52" s="39" t="s">
-        <v>388</v>
+        <v>223</v>
+      </c>
+      <c r="I52" s="57" t="s">
+        <v>406</v>
       </c>
       <c r="J52" s="26"/>
       <c r="K52" s="16"/>
@@ -5052,12 +5304,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446EB1FC-0FB5-4845-B71D-73D3B9D3439E}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="15.25" defaultRowHeight="63" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="96.75" style="45" customWidth="1"/>
+    <col min="3" max="3" width="96.75" style="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
@@ -5065,158 +5317,202 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>89</v>
+      <c r="B2" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>382</v>
+        <v>330</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>328</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>104</v>
+      <c r="B4" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>103</v>
+        <v>342</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>182</v>
+        <v>343</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>146</v>
+        <v>154</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>181</v>
+        <v>349</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>369</v>
+        <v>412</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
-        <v>367</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>370</v>
+        <v>146</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>171</v>
+        <v>344</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>380</v>
+        <v>366</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>93</v>
+        <v>101</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>87</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>93</v>
+        <v>305</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>87</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>350</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="59" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="59" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="C17" s="59" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C14" xr:uid="{446EB1FC-0FB5-4845-B71D-73D3B9D3439E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C14">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C18">
       <sortCondition ref="B1:B14"/>
     </sortState>
   </autoFilter>
@@ -5232,26 +5528,26 @@
   <cols>
     <col min="1" max="1" width="19" style="26"/>
     <col min="2" max="2" width="19" style="16"/>
-    <col min="3" max="3" width="79.375" style="49" customWidth="1"/>
+    <col min="3" max="3" width="79.375" style="47" customWidth="1"/>
     <col min="4" max="16384" width="19" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="51" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="49" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>392</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
-        <v>393</v>
-      </c>
-      <c r="B2" s="47" t="s">
+      <c r="A2" s="56" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="38" t="s">
@@ -5259,8 +5555,8 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52"/>
-      <c r="B3" s="47" t="s">
+      <c r="A3" s="56"/>
+      <c r="B3" s="45" t="s">
         <v>26</v>
       </c>
       <c r="C3" s="38" t="s">
@@ -5268,15 +5564,15 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48"/>
-      <c r="B4" s="47"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="38"/>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="53" t="s">
-        <v>394</v>
-      </c>
-      <c r="B5" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="38" t="s">
@@ -5285,7 +5581,7 @@
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="54"/>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="45" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="38" t="s">
@@ -5294,41 +5590,41 @@
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="54"/>
-      <c r="B7" s="47" t="s">
-        <v>395</v>
-      </c>
-      <c r="C7" s="50" t="s">
-        <v>396</v>
+      <c r="B7" s="45" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55"/>
-      <c r="B8" s="47" t="s">
-        <v>209</v>
+      <c r="B8" s="45" t="s">
+        <v>176</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="47"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="38"/>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="53" t="s">
-        <v>397</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>69</v>
+        <v>340</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>67</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="54"/>
-      <c r="B11" s="47" t="s">
-        <v>210</v>
+      <c r="B11" s="45" t="s">
+        <v>177</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>37</v>
@@ -5336,7 +5632,7 @@
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="54"/>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="45" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="38" t="s">
@@ -5345,8 +5641,8 @@
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="54"/>
-      <c r="B13" s="47" t="s">
-        <v>211</v>
+      <c r="B13" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>36</v>
@@ -5354,8 +5650,8 @@
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="54"/>
-      <c r="B14" s="47" t="s">
-        <v>212</v>
+      <c r="B14" s="45" t="s">
+        <v>179</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>38</v>
@@ -5363,8 +5659,8 @@
     </row>
     <row r="15" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="54"/>
-      <c r="B15" s="47" t="s">
-        <v>213</v>
+      <c r="B15" s="45" t="s">
+        <v>180</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>43</v>
@@ -5372,8 +5668,8 @@
     </row>
     <row r="16" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="54"/>
-      <c r="B16" s="47" t="s">
-        <v>214</v>
+      <c r="B16" s="45" t="s">
+        <v>181</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>39</v>
@@ -5381,8 +5677,8 @@
     </row>
     <row r="17" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="54"/>
-      <c r="B17" s="47" t="s">
-        <v>215</v>
+      <c r="B17" s="45" t="s">
+        <v>182</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>41</v>
@@ -5390,8 +5686,8 @@
     </row>
     <row r="18" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="54"/>
-      <c r="B18" s="47" t="s">
-        <v>216</v>
+      <c r="B18" s="45" t="s">
+        <v>183</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>42</v>
@@ -5399,8 +5695,8 @@
     </row>
     <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
-      <c r="B19" s="47" t="s">
-        <v>217</v>
+      <c r="B19" s="45" t="s">
+        <v>184</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>40</v>
@@ -5408,7 +5704,7 @@
     </row>
     <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="54"/>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="45" t="s">
         <v>47</v>
       </c>
       <c r="C20" s="38" t="s">
@@ -5417,79 +5713,79 @@
     </row>
     <row r="21" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="54"/>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="38" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="55"/>
-      <c r="B22" s="47" t="s">
-        <v>118</v>
+      <c r="B22" s="45" t="s">
+        <v>104</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="53" t="s">
-        <v>398</v>
-      </c>
-      <c r="B24" s="47" t="s">
-        <v>61</v>
+        <v>341</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>59</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="54"/>
-      <c r="B25" s="47" t="s">
-        <v>62</v>
+      <c r="B25" s="45" t="s">
+        <v>60</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="54"/>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="38" t="s">
         <v>63</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="54"/>
-      <c r="B27" s="47" t="s">
-        <v>218</v>
+      <c r="B27" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="55"/>
-      <c r="B28" s="47" t="s">
-        <v>219</v>
+      <c r="B28" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="47"/>
+      <c r="B30" s="45"/>
       <c r="C30" s="38"/>
     </row>
     <row r="31" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="47"/>
+      <c r="B31" s="45"/>
       <c r="C31" s="38"/>
     </row>
     <row r="32" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="47"/>
+      <c r="B32" s="45"/>
       <c r="C32" s="38"/>
     </row>
   </sheetData>
@@ -5520,163 +5816,163 @@
     <row r="1" spans="1:6" s="2" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="53" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>390</v>
+        <v>191</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>333</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>402</v>
+        <v>345</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="54"/>
       <c r="B3" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" s="58"/>
+        <v>191</v>
+      </c>
+      <c r="C3" s="52"/>
       <c r="D3" s="54"/>
       <c r="E3" s="36" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="54"/>
       <c r="B4" s="36" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="54"/>
-      <c r="E4" s="56" t="s">
-        <v>222</v>
+      <c r="E4" s="50" t="s">
+        <v>189</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="54"/>
       <c r="B5" s="36" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="54"/>
-      <c r="E5" s="57"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="36" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="54"/>
       <c r="B6" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>391</v>
+        <v>194</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>334</v>
       </c>
       <c r="D6" s="54"/>
-      <c r="E6" s="58"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="36" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="55"/>
       <c r="B7" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="58"/>
+        <v>194</v>
+      </c>
+      <c r="C7" s="52"/>
       <c r="D7" s="54"/>
-      <c r="E7" s="56" t="s">
-        <v>228</v>
+      <c r="E7" s="50" t="s">
+        <v>195</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="54"/>
-      <c r="E8" s="57"/>
+      <c r="E8" s="51"/>
       <c r="F8" s="36" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="54"/>
-      <c r="E9" s="58"/>
+      <c r="E9" s="52"/>
       <c r="F9" s="36" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="54"/>
-      <c r="E10" s="56" t="s">
-        <v>229</v>
+      <c r="E10" s="50" t="s">
+        <v>196</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="54"/>
-      <c r="E11" s="57"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="36" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="54"/>
-      <c r="E12" s="58"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="36" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="54"/>
-      <c r="E13" s="56" t="s">
-        <v>230</v>
+      <c r="E13" s="50" t="s">
+        <v>197</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="54"/>
-      <c r="E14" s="57"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="36" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D15" s="54"/>
-      <c r="E15" s="58"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="36" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="55"/>
       <c r="E16" s="36" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
